--- a/gcam-data-system/energy-data/assumptions/Tables_A52s.xlsx
+++ b/gcam-data-system/energy-data/assumptions/Tables_A52s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="23416"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="0" windowWidth="25360" windowHeight="15780" tabRatio="684" firstSheet="3" activeTab="7"/>
+    <workbookView xWindow="240" yWindow="0" windowWidth="25360" windowHeight="15780" tabRatio="684" firstSheet="3" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="A52.sector.csv" sheetId="5" r:id="rId1"/>
@@ -148,9 +148,6 @@
     <t>elect_td_trn</t>
   </si>
   <si>
-    <t>H2 Enduse</t>
-  </si>
-  <si>
     <t># Transportation sector default supplysector information (units and logit exponents)</t>
   </si>
   <si>
@@ -170,6 +167,9 @@
   </si>
   <si>
     <t># Transportation technology default shareweights</t>
+  </si>
+  <si>
+    <t>H2 enduse</t>
   </si>
 </sst>
 </file>
@@ -4178,7 +4178,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -4238,7 +4238,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4332,7 +4332,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -4449,7 +4449,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -4603,7 +4603,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4755,7 +4755,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -4828,7 +4828,7 @@
         <v>0.48</v>
       </c>
       <c r="F4" s="1">
-        <f t="shared" ref="F4:G4" si="0">F6*3</f>
+        <f t="shared" ref="F4" si="0">F6*3</f>
         <v>0.51</v>
       </c>
       <c r="G4" s="1">
@@ -4852,7 +4852,7 @@
         <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E5" s="1">
         <f>E7*1.4</f>
@@ -4961,7 +4961,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6">

--- a/gcam-data-system/energy-data/assumptions/Tables_A52s.xlsx
+++ b/gcam-data-system/energy-data/assumptions/Tables_A52s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="23416"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="0" windowWidth="25360" windowHeight="15780" tabRatio="684" firstSheet="3" activeTab="5"/>
+    <workbookView xWindow="240" yWindow="0" windowWidth="25360" windowHeight="15780" tabRatio="684" firstSheet="2" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="A52.sector.csv" sheetId="5" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="49">
   <si>
     <t>technology</t>
   </si>
@@ -171,6 +171,9 @@
   <si>
     <t>H2 enduse</t>
   </si>
+  <si>
+    <t>final.energy</t>
+  </si>
 </sst>
 </file>
 
@@ -221,8 +224,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1805">
+  <cellStyleXfs count="1817">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2032,7 +2047,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1805">
+  <cellStyles count="1817">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
@@ -2935,6 +2950,12 @@
     <cellStyle name="Followed Hyperlink" xfId="1800" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="1802" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="1804" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1806" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1808" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1810" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1812" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1814" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1816" builtinId="9" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
@@ -3837,6 +3858,12 @@
     <cellStyle name="Hyperlink" xfId="1799" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1801" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1803" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1805" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1807" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1809" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1811" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1813" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1815" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4166,7 +4193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
@@ -4176,12 +4203,12 @@
     <col min="5" max="5" width="13.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -4197,8 +4224,11 @@
       <c r="E2" t="s">
         <v>6</v>
       </c>
+      <c r="F2" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -4213,6 +4243,9 @@
       </c>
       <c r="E3">
         <v>-1.5</v>
+      </c>
+      <c r="F3" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -4320,7 +4353,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
@@ -4387,11 +4420,11 @@
       <c r="B5" t="s">
         <v>37</v>
       </c>
-      <c r="C5" t="s">
-        <v>17</v>
+      <c r="D5">
+        <v>2020</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4399,13 +4432,13 @@
         <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
+        <v>37</v>
+      </c>
+      <c r="C6">
+        <v>2050</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4413,12 +4446,26 @@
         <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
         <v>17</v>
       </c>
       <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8">
         <v>1</v>
       </c>
     </row>
@@ -4530,9 +4577,6 @@
       </c>
       <c r="E5">
         <v>2050</v>
-      </c>
-      <c r="F5">
-        <v>0.5</v>
       </c>
       <c r="G5" t="s">
         <v>38</v>
@@ -4948,7 +4992,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
@@ -4959,12 +5003,12 @@
     <col min="6" max="6" width="5.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -4978,13 +5022,16 @@
         <v>1971</v>
       </c>
       <c r="E2">
+        <v>2019</v>
+      </c>
+      <c r="F2">
         <v>2020</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>2100</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -5003,8 +5050,11 @@
       <c r="F3">
         <v>1</v>
       </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -5023,8 +5073,11 @@
       <c r="F4">
         <v>1</v>
       </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -5043,8 +5096,11 @@
       <c r="F5">
         <v>1</v>
       </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -5063,8 +5119,11 @@
       <c r="F6">
         <v>1</v>
       </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -5081,6 +5140,9 @@
         <v>1</v>
       </c>
       <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
     </row>
